--- a/ExcelFiles/TestAutomation.xlsx
+++ b/ExcelFiles/TestAutomation.xlsx
@@ -20,12 +20,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
+  <si>
+    <t xml:space="preserve">Username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password</t>
+  </si>
   <si>
     <t xml:space="preserve">raster</t>
   </si>
   <si>
-    <t xml:space="preserve">irast45</t>
+    <t xml:space="preserve">raster0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS%^&amp;#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
 </sst>
 </file>
@@ -35,7 +53,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -57,6 +75,21 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -101,8 +134,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -123,26 +164,82 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
